--- a/data/sites.xlsx
+++ b/data/sites.xlsx
@@ -1,28 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Temp\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="12" windowWidth="16092" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$94</definedName>
-  </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="248">
   <si>
     <t>site_name</t>
   </si>
@@ -745,6 +737,9 @@
   </si>
   <si>
     <t>customs_tax</t>
+  </si>
+  <si>
+    <t>OK</t>
   </si>
   <si>
     <t>FAIL</t>
@@ -768,15 +763,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -786,13 +781,6 @@
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -819,31 +807,22 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -885,7 +864,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -917,10 +896,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -952,7 +930,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1128,20 +1105,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N94"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="19.5" customWidth="1"/>
-    <col min="3" max="3" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.09765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="7" customWidth="1"/>
-    <col min="8" max="10" width="5.19921875" customWidth="1"/>
-    <col min="12" max="12" width="12.3984375" style="3" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1175,7 +1143,7 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -1185,7 +1153,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1214,22 +1182,22 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3">
-        <v>46152.423449074071</v>
+        <v>20</v>
+      </c>
+      <c r="L2" s="2">
+        <v>46155.02611111111</v>
       </c>
       <c r="M2" t="s">
         <v>241</v>
       </c>
       <c r="N2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -1258,22 +1226,22 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="L3" s="2">
-        <v>46152.423472222217</v>
+        <v>46155.02613425926</v>
       </c>
       <c r="M3" t="s">
         <v>241</v>
       </c>
       <c r="N3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1302,22 +1270,22 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K4">
-        <v>274</v>
+        <v>306</v>
       </c>
       <c r="L4" s="2">
-        <v>46152.423495370371</v>
+        <v>46155.02615740741</v>
       </c>
       <c r="M4" t="s">
         <v>241</v>
       </c>
       <c r="N4" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1346,22 +1314,22 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K5">
-        <v>339</v>
+        <v>433</v>
       </c>
       <c r="L5" s="2">
-        <v>46152.423506944448</v>
+        <v>46155.02616898148</v>
       </c>
       <c r="M5" t="s">
         <v>241</v>
       </c>
       <c r="N5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1390,22 +1358,22 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3">
-        <v>46152.423518518517</v>
+        <v>6</v>
+      </c>
+      <c r="L6" s="2">
+        <v>46155.02618055556</v>
       </c>
       <c r="M6" t="s">
         <v>241</v>
       </c>
       <c r="N6" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1439,17 +1407,17 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="L7" s="3">
-        <v>46152.423530092587</v>
+      <c r="L7" s="2">
+        <v>46155.0262037037</v>
       </c>
       <c r="M7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1483,17 +1451,17 @@
       <c r="K8">
         <v>0</v>
       </c>
-      <c r="L8" s="3">
-        <v>46152.423530092587</v>
+      <c r="L8" s="2">
+        <v>46155.02621527778</v>
       </c>
       <c r="M8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N8">
         <v>4.2</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1527,17 +1495,17 @@
       <c r="K9">
         <v>0</v>
       </c>
-      <c r="L9" s="3">
-        <v>46152.423541666663</v>
+      <c r="L9" s="2">
+        <v>46155.02621527778</v>
       </c>
       <c r="M9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N9" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1571,17 +1539,17 @@
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="L10" s="3">
-        <v>46152.423541666663</v>
+      <c r="L10" s="2">
+        <v>46155.02621527778</v>
       </c>
       <c r="M10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N10" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1610,22 +1578,22 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="L11" s="2">
-        <v>46152.423564814817</v>
+        <v>46155.02622685185</v>
       </c>
       <c r="M11" t="s">
         <v>241</v>
       </c>
       <c r="N11" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -1654,22 +1622,22 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="L12" s="2">
-        <v>46152.423576388886</v>
+        <v>46155.02622685185</v>
       </c>
       <c r="M12" t="s">
         <v>241</v>
       </c>
       <c r="N12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1698,22 +1666,22 @@
         <v>1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="L13" s="2">
-        <v>46152.423576388886</v>
+        <v>46155.02622685185</v>
       </c>
       <c r="M13" t="s">
         <v>241</v>
       </c>
       <c r="N13" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1742,22 +1710,22 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="L14" s="2">
-        <v>46152.423576388886</v>
+        <v>46155.02623842593</v>
       </c>
       <c r="M14" t="s">
         <v>241</v>
       </c>
       <c r="N14" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -1786,22 +1754,22 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="L15" s="2">
-        <v>46152.423587962963</v>
+        <v>46155.02623842593</v>
       </c>
       <c r="M15" t="s">
         <v>241</v>
       </c>
       <c r="N15" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -1835,17 +1803,17 @@
       <c r="K16">
         <v>0</v>
       </c>
-      <c r="L16" s="3">
-        <v>46152.423587962963</v>
+      <c r="L16" s="2">
+        <v>46155.02625</v>
       </c>
       <c r="M16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N16">
         <v>4.2</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1874,13 +1842,13 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3">
-        <v>46152.423587962963</v>
+        <v>20</v>
+      </c>
+      <c r="L17" s="2">
+        <v>46155.02625</v>
       </c>
       <c r="M17" t="s">
         <v>241</v>
@@ -1889,7 +1857,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -1918,13 +1886,13 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3">
-        <v>46152.42359953704</v>
+        <v>20</v>
+      </c>
+      <c r="L18" s="2">
+        <v>46155.02626157407</v>
       </c>
       <c r="M18" t="s">
         <v>241</v>
@@ -1933,7 +1901,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -1967,17 +1935,17 @@
       <c r="K19">
         <v>0</v>
       </c>
-      <c r="L19" s="3">
-        <v>46152.42359953704</v>
+      <c r="L19" s="2">
+        <v>46155.02627314815</v>
       </c>
       <c r="M19" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N19" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -2006,22 +1974,22 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>46152.42359953704</v>
+        <v>20</v>
+      </c>
+      <c r="L20" s="2">
+        <v>46155.02628472223</v>
       </c>
       <c r="M20" t="s">
         <v>241</v>
       </c>
       <c r="N20" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -2050,13 +2018,13 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3">
-        <v>46152.423611111109</v>
+        <v>20</v>
+      </c>
+      <c r="L21" s="2">
+        <v>46155.0262962963</v>
       </c>
       <c r="M21" t="s">
         <v>241</v>
@@ -2065,7 +2033,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -2094,13 +2062,13 @@
         <v>1</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>46152.423622685194</v>
+        <v>20</v>
+      </c>
+      <c r="L22" s="2">
+        <v>46155.0262962963</v>
       </c>
       <c r="M22" t="s">
         <v>241</v>
@@ -2109,7 +2077,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
         <v>35</v>
       </c>
@@ -2141,19 +2109,19 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L23" s="2">
-        <v>46152.423622685194</v>
+        <v>46155.02630787037</v>
       </c>
       <c r="M23" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N23" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -2187,17 +2155,17 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24" s="3">
-        <v>46152.423622685194</v>
+      <c r="L24" s="2">
+        <v>46155.02630787037</v>
       </c>
       <c r="M24" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -2226,13 +2194,13 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K25">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L25" s="2">
-        <v>46152.423634259263</v>
+        <v>46155.02633101852</v>
       </c>
       <c r="M25" t="s">
         <v>241</v>
@@ -2241,7 +2209,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -2270,13 +2238,13 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3">
-        <v>46152.423634259263</v>
+        <v>12</v>
+      </c>
+      <c r="L26" s="2">
+        <v>46155.0263425926</v>
       </c>
       <c r="M26" t="s">
         <v>241</v>
@@ -2285,7 +2253,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -2314,13 +2282,13 @@
         <v>1</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K27">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="L27" s="2">
-        <v>46152.423645833333</v>
+        <v>46155.02635416666</v>
       </c>
       <c r="M27" t="s">
         <v>241</v>
@@ -2329,7 +2297,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -2358,13 +2326,13 @@
         <v>1</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K28">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="L28" s="2">
-        <v>46152.423645833333</v>
+        <v>46155.02637731482</v>
       </c>
       <c r="M28" t="s">
         <v>241</v>
@@ -2373,7 +2341,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
         <v>41</v>
       </c>
@@ -2402,13 +2370,13 @@
         <v>1</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>46152.423657407409</v>
+        <v>12</v>
+      </c>
+      <c r="L29" s="2">
+        <v>46155.02638888889</v>
       </c>
       <c r="M29" t="s">
         <v>241</v>
@@ -2417,7 +2385,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -2446,13 +2414,13 @@
         <v>1</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K30">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="L30" s="2">
-        <v>46152.423657407409</v>
+        <v>46155.02640046296</v>
       </c>
       <c r="M30" t="s">
         <v>241</v>
@@ -2461,7 +2429,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
         <v>43</v>
       </c>
@@ -2490,13 +2458,13 @@
         <v>1</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K31">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="L31" s="2">
-        <v>46152.423657407409</v>
+        <v>46155.02642361111</v>
       </c>
       <c r="M31" t="s">
         <v>241</v>
@@ -2505,7 +2473,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
         <v>44</v>
       </c>
@@ -2540,16 +2508,16 @@
         <v>23</v>
       </c>
       <c r="L32" s="2">
-        <v>46152.423668981479</v>
+        <v>46155.02642361111</v>
       </c>
       <c r="M32" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N32" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -2578,13 +2546,13 @@
         <v>1</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3">
-        <v>46152.423668981479</v>
+        <v>12</v>
+      </c>
+      <c r="L33" s="2">
+        <v>46155.02644675926</v>
       </c>
       <c r="M33" t="s">
         <v>241</v>
@@ -2593,7 +2561,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
         <v>46</v>
       </c>
@@ -2622,13 +2590,13 @@
         <v>1</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K34">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="L34" s="2">
-        <v>46152.423680555563</v>
+        <v>46155.02644675926</v>
       </c>
       <c r="M34" t="s">
         <v>241</v>
@@ -2637,7 +2605,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
         <v>47</v>
       </c>
@@ -2666,22 +2634,22 @@
         <v>1</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3">
-        <v>46152.423680555563</v>
+        <v>3</v>
+      </c>
+      <c r="L35" s="2">
+        <v>46155.02646990741</v>
       </c>
       <c r="M35" t="s">
         <v>241</v>
       </c>
       <c r="N35" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
         <v>48</v>
       </c>
@@ -2710,13 +2678,13 @@
         <v>1</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K36">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="L36" s="2">
-        <v>46152.423692129632</v>
+        <v>46155.02646990741</v>
       </c>
       <c r="M36" t="s">
         <v>241</v>
@@ -2725,7 +2693,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
         <v>49</v>
       </c>
@@ -2754,13 +2722,13 @@
         <v>1</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K37">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="L37" s="2">
-        <v>46152.423692129632</v>
+        <v>46155.02648148148</v>
       </c>
       <c r="M37" t="s">
         <v>241</v>
@@ -2769,7 +2737,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
         <v>50</v>
       </c>
@@ -2798,22 +2766,22 @@
         <v>1</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38" s="3">
-        <v>46152.423703703702</v>
+        <v>3</v>
+      </c>
+      <c r="L38" s="2">
+        <v>46155.02649305556</v>
       </c>
       <c r="M38" t="s">
         <v>241</v>
       </c>
       <c r="N38" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
         <v>51</v>
       </c>
@@ -2842,22 +2810,22 @@
         <v>1</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K39">
-        <v>0</v>
-      </c>
-      <c r="L39" s="3">
-        <v>46152.423703703702</v>
+        <v>3</v>
+      </c>
+      <c r="L39" s="2">
+        <v>46155.0265162037</v>
       </c>
       <c r="M39" t="s">
         <v>241</v>
       </c>
       <c r="N39" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
         <v>52</v>
       </c>
@@ -2886,13 +2854,13 @@
         <v>1</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K40">
-        <v>217</v>
+        <v>295</v>
       </c>
       <c r="L40" s="2">
-        <v>46152.423715277779</v>
+        <v>46155.02652777778</v>
       </c>
       <c r="M40" t="s">
         <v>241</v>
@@ -2901,7 +2869,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
         <v>53</v>
       </c>
@@ -2930,13 +2898,13 @@
         <v>1</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41">
-        <v>366</v>
+        <v>465</v>
       </c>
       <c r="L41" s="2">
-        <v>46152.423726851863</v>
+        <v>46155.02653935185</v>
       </c>
       <c r="M41" t="s">
         <v>241</v>
@@ -2945,7 +2913,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
         <v>54</v>
       </c>
@@ -2974,13 +2942,13 @@
         <v>1</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K42">
-        <v>417</v>
+        <v>501</v>
       </c>
       <c r="L42" s="2">
-        <v>46152.423738425918</v>
+        <v>46155.0265625</v>
       </c>
       <c r="M42" t="s">
         <v>241</v>
@@ -2989,7 +2957,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
         <v>55</v>
       </c>
@@ -3018,13 +2986,13 @@
         <v>1</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K43">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>46152.423761574071</v>
+        <v>19</v>
+      </c>
+      <c r="L43" s="2">
+        <v>46155.02659722222</v>
       </c>
       <c r="M43" t="s">
         <v>241</v>
@@ -3033,7 +3001,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
         <v>56</v>
       </c>
@@ -3062,13 +3030,13 @@
         <v>1</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K44">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="L44" s="2">
-        <v>46152.423761574071</v>
+        <v>46155.02659722222</v>
       </c>
       <c r="M44" t="s">
         <v>241</v>
@@ -3077,7 +3045,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
         <v>57</v>
       </c>
@@ -3106,13 +3074,13 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K45">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3">
-        <v>46152.423773148148</v>
+        <v>20</v>
+      </c>
+      <c r="L45" s="2">
+        <v>46155.0266087963</v>
       </c>
       <c r="M45" t="s">
         <v>241</v>
@@ -3121,7 +3089,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
         <v>58</v>
       </c>
@@ -3150,13 +3118,13 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3">
-        <v>46152.423784722218</v>
+        <v>20</v>
+      </c>
+      <c r="L46" s="2">
+        <v>46155.02662037037</v>
       </c>
       <c r="M46" t="s">
         <v>241</v>
@@ -3165,7 +3133,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
         <v>59</v>
       </c>
@@ -3194,13 +3162,13 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>46152.423784722218</v>
+        <v>20</v>
+      </c>
+      <c r="L47" s="2">
+        <v>46155.02664351852</v>
       </c>
       <c r="M47" t="s">
         <v>241</v>
@@ -3209,7 +3177,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
         <v>60</v>
       </c>
@@ -3238,22 +3206,22 @@
         <v>1</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3">
-        <v>46152.423796296287</v>
+        <v>19</v>
+      </c>
+      <c r="L48" s="2">
+        <v>46155.0266550926</v>
       </c>
       <c r="M48" t="s">
         <v>241</v>
       </c>
       <c r="N48" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" t="s">
         <v>61</v>
       </c>
@@ -3282,13 +3250,13 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K49">
-        <v>199</v>
+        <v>249</v>
       </c>
       <c r="L49" s="2">
-        <v>46152.423807870371</v>
+        <v>46155.02667824074</v>
       </c>
       <c r="M49" t="s">
         <v>241</v>
@@ -3297,7 +3265,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:14">
       <c r="A50" t="s">
         <v>62</v>
       </c>
@@ -3326,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K50">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="L50" s="2">
-        <v>46152.423831018517</v>
+        <v>46155.02668981482</v>
       </c>
       <c r="M50" t="s">
         <v>241</v>
@@ -3341,7 +3309,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:14">
       <c r="A51" t="s">
         <v>63</v>
       </c>
@@ -3370,13 +3338,13 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51" s="3">
-        <v>46152.423842592587</v>
+        <v>10</v>
+      </c>
+      <c r="L51" s="2">
+        <v>46155.02671296296</v>
       </c>
       <c r="M51" t="s">
         <v>241</v>
@@ -3385,7 +3353,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:14">
       <c r="A52" t="s">
         <v>64</v>
       </c>
@@ -3419,17 +3387,17 @@
       <c r="K52">
         <v>0</v>
       </c>
-      <c r="L52" s="3">
-        <v>46152.423842592587</v>
+      <c r="L52" s="2">
+        <v>46155.02672453703</v>
       </c>
       <c r="M52" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N52" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" t="s">
         <v>65</v>
       </c>
@@ -3458,13 +3426,13 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K53">
-        <v>0</v>
-      </c>
-      <c r="L53" s="3">
-        <v>46152.423854166656</v>
+        <v>22</v>
+      </c>
+      <c r="L53" s="2">
+        <v>46155.02673611111</v>
       </c>
       <c r="M53" t="s">
         <v>241</v>
@@ -3473,7 +3441,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:14">
       <c r="A54" t="s">
         <v>66</v>
       </c>
@@ -3502,22 +3470,22 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K54">
-        <v>0</v>
-      </c>
-      <c r="L54" s="3">
-        <v>46152.42386574074</v>
+        <v>6</v>
+      </c>
+      <c r="L54" s="2">
+        <v>46155.02675925926</v>
       </c>
       <c r="M54" t="s">
         <v>241</v>
       </c>
       <c r="N54" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" t="s">
         <v>67</v>
       </c>
@@ -3546,22 +3514,22 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K55">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L55" s="2">
-        <v>46152.423877314817</v>
+        <v>46155.02677083333</v>
       </c>
       <c r="M55" t="s">
         <v>241</v>
       </c>
       <c r="N55" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56" t="s">
         <v>68</v>
       </c>
@@ -3590,13 +3558,13 @@
         <v>1</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K56">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="L56" s="2">
-        <v>46152.423888888887</v>
+        <v>46155.02677083333</v>
       </c>
       <c r="M56" t="s">
         <v>241</v>
@@ -3605,7 +3573,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:14">
       <c r="A57" t="s">
         <v>69</v>
       </c>
@@ -3634,13 +3602,13 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K57">
-        <v>278</v>
+        <v>351</v>
       </c>
       <c r="L57" s="2">
-        <v>46152.423888888887</v>
+        <v>46155.02678240741</v>
       </c>
       <c r="M57" t="s">
         <v>241</v>
@@ -3649,7 +3617,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:14">
       <c r="A58" t="s">
         <v>70</v>
       </c>
@@ -3678,13 +3646,13 @@
         <v>1</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K58">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="L58" s="2">
-        <v>46152.423900462964</v>
+        <v>46155.02679398148</v>
       </c>
       <c r="M58" t="s">
         <v>241</v>
@@ -3693,7 +3661,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:14">
       <c r="A59" t="s">
         <v>71</v>
       </c>
@@ -3722,13 +3690,13 @@
         <v>1</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K59">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3">
-        <v>46152.42392361111</v>
+        <v>20</v>
+      </c>
+      <c r="L59" s="2">
+        <v>46155.0268287037</v>
       </c>
       <c r="M59" t="s">
         <v>241</v>
@@ -3737,7 +3705,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:14">
       <c r="A60" t="s">
         <v>72</v>
       </c>
@@ -3766,13 +3734,13 @@
         <v>1</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K60">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3">
-        <v>46152.423935185187</v>
+        <v>20</v>
+      </c>
+      <c r="L60" s="2">
+        <v>46155.02684027778</v>
       </c>
       <c r="M60" t="s">
         <v>241</v>
@@ -3781,7 +3749,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:14">
       <c r="A61" t="s">
         <v>73</v>
       </c>
@@ -3815,17 +3783,17 @@
       <c r="K61">
         <v>0</v>
       </c>
-      <c r="L61" s="3">
-        <v>46152.423935185187</v>
+      <c r="L61" s="2">
+        <v>46155.02685185185</v>
       </c>
       <c r="M61" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N61" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.4">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
       <c r="A62" t="s">
         <v>74</v>
       </c>
@@ -3854,13 +3822,13 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K62">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
-        <v>46152.423946759263</v>
+        <v>6</v>
+      </c>
+      <c r="L62" s="2">
+        <v>46155.02685185185</v>
       </c>
       <c r="M62" t="s">
         <v>241</v>
@@ -3869,7 +3837,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:14">
       <c r="A63" t="s">
         <v>75</v>
       </c>
@@ -3898,13 +3866,13 @@
         <v>1</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K63">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="L63" s="2">
-        <v>46152.423946759263</v>
+        <v>46155.02686342593</v>
       </c>
       <c r="M63" t="s">
         <v>241</v>
@@ -3913,7 +3881,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:14">
       <c r="A64" t="s">
         <v>76</v>
       </c>
@@ -3947,17 +3915,17 @@
       <c r="K64">
         <v>0</v>
       </c>
-      <c r="L64" s="3">
-        <v>46152.424189814818</v>
+      <c r="L64" s="2">
+        <v>46155.02710648148</v>
       </c>
       <c r="M64" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N64" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.4">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
       <c r="A65" t="s">
         <v>77</v>
       </c>
@@ -3986,22 +3954,22 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K65">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="L65" s="2">
-        <v>46152.424201388887</v>
+        <v>46155.02715277778</v>
       </c>
       <c r="M65" t="s">
         <v>241</v>
       </c>
       <c r="N65" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.4">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
       <c r="A66" t="s">
         <v>78</v>
       </c>
@@ -4030,13 +3998,13 @@
         <v>1</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K66">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="L66" s="2">
-        <v>46152.424212962957</v>
+        <v>46155.02716435185</v>
       </c>
       <c r="M66" t="s">
         <v>241</v>
@@ -4045,7 +4013,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:14">
       <c r="A67" t="s">
         <v>79</v>
       </c>
@@ -4079,17 +4047,17 @@
       <c r="K67">
         <v>0</v>
       </c>
-      <c r="L67" s="3">
-        <v>46152.424212962957</v>
+      <c r="L67" s="2">
+        <v>46155.02716435185</v>
       </c>
       <c r="M67" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N67" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.4">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
       <c r="A68" t="s">
         <v>80</v>
       </c>
@@ -4123,17 +4091,17 @@
       <c r="K68">
         <v>0</v>
       </c>
-      <c r="L68" s="3">
-        <v>46152.424212962957</v>
+      <c r="L68" s="2">
+        <v>46155.02717592593</v>
       </c>
       <c r="M68" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N68" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.4">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
       <c r="A69" t="s">
         <v>81</v>
       </c>
@@ -4165,19 +4133,19 @@
         <v>0</v>
       </c>
       <c r="K69">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="L69" s="2">
-        <v>46152.424259259264</v>
+        <v>46155.02741898148</v>
       </c>
       <c r="M69" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N69" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:14">
       <c r="A70" t="s">
         <v>82</v>
       </c>
@@ -4211,17 +4179,17 @@
       <c r="K70">
         <v>0</v>
       </c>
-      <c r="L70" s="3">
-        <v>46152.424340277779</v>
+      <c r="L70" s="2">
+        <v>46155.02767361111</v>
       </c>
       <c r="M70" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N70" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:14">
       <c r="A71" t="s">
         <v>83</v>
       </c>
@@ -4255,17 +4223,17 @@
       <c r="K71">
         <v>0</v>
       </c>
-      <c r="L71" s="3">
-        <v>46152.424398148149</v>
+      <c r="L71" s="2">
+        <v>46155.02791666667</v>
       </c>
       <c r="M71" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N71" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:14">
       <c r="A72" t="s">
         <v>84</v>
       </c>
@@ -4294,13 +4262,13 @@
         <v>1</v>
       </c>
       <c r="J72">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K72">
-        <v>0</v>
-      </c>
-      <c r="L72" s="3">
-        <v>46152.424409722233</v>
+        <v>20</v>
+      </c>
+      <c r="L72" s="2">
+        <v>46155.02793981481</v>
       </c>
       <c r="M72" t="s">
         <v>241</v>
@@ -4309,7 +4277,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:14">
       <c r="A73" t="s">
         <v>85</v>
       </c>
@@ -4343,17 +4311,17 @@
       <c r="K73">
         <v>0</v>
       </c>
-      <c r="L73" s="3">
-        <v>46152.424432870372</v>
+      <c r="L73" s="2">
+        <v>46155.02796296297</v>
       </c>
       <c r="M73" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N73" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.4">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
       <c r="A74" t="s">
         <v>86</v>
       </c>
@@ -4382,13 +4350,13 @@
         <v>1</v>
       </c>
       <c r="J74">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K74">
-        <v>0</v>
-      </c>
-      <c r="L74" s="3">
-        <v>46152.424456018518</v>
+        <v>20</v>
+      </c>
+      <c r="L74" s="2">
+        <v>46155.02798611111</v>
       </c>
       <c r="M74" t="s">
         <v>241</v>
@@ -4397,7 +4365,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:14">
       <c r="A75" t="s">
         <v>87</v>
       </c>
@@ -4426,13 +4394,13 @@
         <v>1</v>
       </c>
       <c r="J75">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K75">
-        <v>0</v>
-      </c>
-      <c r="L75" s="3">
-        <v>46152.424456018518</v>
+        <v>20</v>
+      </c>
+      <c r="L75" s="2">
+        <v>46155.02799768518</v>
       </c>
       <c r="M75" t="s">
         <v>241</v>
@@ -4441,7 +4409,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:14">
       <c r="A76" t="s">
         <v>88</v>
       </c>
@@ -4470,13 +4438,13 @@
         <v>1</v>
       </c>
       <c r="J76">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K76">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="L76" s="2">
-        <v>46152.424467592587</v>
+        <v>46155.02800925926</v>
       </c>
       <c r="M76" t="s">
         <v>241</v>
@@ -4485,7 +4453,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:14">
       <c r="A77" t="s">
         <v>89</v>
       </c>
@@ -4514,13 +4482,13 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K77">
-        <v>0</v>
-      </c>
-      <c r="L77" s="3">
-        <v>46152.424479166657</v>
+        <v>20</v>
+      </c>
+      <c r="L77" s="2">
+        <v>46155.02802083334</v>
       </c>
       <c r="M77" t="s">
         <v>241</v>
@@ -4529,7 +4497,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:14">
       <c r="A78" t="s">
         <v>90</v>
       </c>
@@ -4563,17 +4531,17 @@
       <c r="K78">
         <v>0</v>
       </c>
-      <c r="L78" s="3">
-        <v>46152.424479166657</v>
+      <c r="L78" s="2">
+        <v>46155.0280324074</v>
       </c>
       <c r="M78" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N78" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.4">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
       <c r="A79" t="s">
         <v>91</v>
       </c>
@@ -4607,17 +4575,17 @@
       <c r="K79">
         <v>0</v>
       </c>
-      <c r="L79" s="3">
-        <v>46152.424490740741</v>
+      <c r="L79" s="2">
+        <v>46155.02804398148</v>
       </c>
       <c r="M79" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N79" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.4">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14">
       <c r="A80" t="s">
         <v>92</v>
       </c>
@@ -4651,17 +4619,17 @@
       <c r="K80">
         <v>0</v>
       </c>
-      <c r="L80" s="3">
-        <v>46152.424502314818</v>
+      <c r="L80" s="2">
+        <v>46155.02804398148</v>
       </c>
       <c r="M80" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N80" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.4">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
       <c r="A81" t="s">
         <v>93</v>
       </c>
@@ -4690,13 +4658,13 @@
         <v>1</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K81">
-        <v>338</v>
+        <v>395</v>
       </c>
       <c r="L81" s="2">
-        <v>46152.424513888887</v>
+        <v>46155.02806712963</v>
       </c>
       <c r="M81" t="s">
         <v>241</v>
@@ -4705,7 +4673,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:14">
       <c r="A82" t="s">
         <v>94</v>
       </c>
@@ -4734,13 +4702,13 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K82">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="L82" s="2">
-        <v>46152.424537037034</v>
+        <v>46155.02809027778</v>
       </c>
       <c r="M82" t="s">
         <v>241</v>
@@ -4749,7 +4717,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:14">
       <c r="A83" t="s">
         <v>95</v>
       </c>
@@ -4783,17 +4751,17 @@
       <c r="K83">
         <v>0</v>
       </c>
-      <c r="L83" s="3">
-        <v>46152.424537037034</v>
+      <c r="L83" s="2">
+        <v>46155.02810185185</v>
       </c>
       <c r="M83" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N83" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.4">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14">
       <c r="A84" t="s">
         <v>96</v>
       </c>
@@ -4827,17 +4795,17 @@
       <c r="K84">
         <v>0</v>
       </c>
-      <c r="L84" s="3">
-        <v>46152.42454861111</v>
+      <c r="L84" s="2">
+        <v>46155.02810185185</v>
       </c>
       <c r="M84" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N84" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.4">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
       <c r="A85" t="s">
         <v>97</v>
       </c>
@@ -4866,22 +4834,22 @@
         <v>1</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K85">
-        <v>0</v>
-      </c>
-      <c r="L85" s="3">
-        <v>46152.42454861111</v>
+        <v>20</v>
+      </c>
+      <c r="L85" s="2">
+        <v>46155.02811342593</v>
       </c>
       <c r="M85" t="s">
         <v>241</v>
       </c>
       <c r="N85" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.4">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14">
       <c r="A86" t="s">
         <v>98</v>
       </c>
@@ -4910,19 +4878,19 @@
         <v>1</v>
       </c>
       <c r="J86">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K86">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L86" s="2">
-        <v>46152.424560185187</v>
+        <v>46155.02813657407</v>
       </c>
       <c r="M86" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:14">
       <c r="A87" t="s">
         <v>99</v>
       </c>
@@ -4951,19 +4919,19 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K87">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="L87" s="2">
-        <v>46152.424571759257</v>
+        <v>46155.02815972222</v>
       </c>
       <c r="M87" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:14">
       <c r="A88" t="s">
         <v>100</v>
       </c>
@@ -4997,14 +4965,14 @@
       <c r="K88">
         <v>0</v>
       </c>
-      <c r="L88" s="3">
-        <v>46152.424583333333</v>
+      <c r="L88" s="2">
+        <v>46155.02818287037</v>
       </c>
       <c r="M88" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.4">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14">
       <c r="A89" t="s">
         <v>101</v>
       </c>
@@ -5029,9 +4997,8 @@
       <c r="H89">
         <v>5</v>
       </c>
-      <c r="L89"/>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.4">
+    </row>
+    <row r="90" spans="1:14">
       <c r="A90" t="s">
         <v>102</v>
       </c>
@@ -5056,9 +5023,8 @@
       <c r="H90">
         <v>5</v>
       </c>
-      <c r="L90"/>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.4">
+    </row>
+    <row r="91" spans="1:14">
       <c r="A91" t="s">
         <v>103</v>
       </c>
@@ -5087,19 +5053,19 @@
         <v>1</v>
       </c>
       <c r="J91">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K91">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>46152.42459490741</v>
+        <v>20</v>
+      </c>
+      <c r="L91" s="2">
+        <v>46155.02819444444</v>
       </c>
       <c r="M91" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:14">
       <c r="A92" t="s">
         <v>104</v>
       </c>
@@ -5128,19 +5094,19 @@
         <v>1</v>
       </c>
       <c r="J92">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K92">
-        <v>0</v>
-      </c>
-      <c r="L92" s="3">
-        <v>46152.42460648148</v>
+        <v>20</v>
+      </c>
+      <c r="L92" s="2">
+        <v>46155.02820601852</v>
       </c>
       <c r="M92" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:14">
       <c r="A93" t="s">
         <v>105</v>
       </c>
@@ -5169,19 +5135,19 @@
         <v>1</v>
       </c>
       <c r="J93">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K93">
-        <v>0</v>
-      </c>
-      <c r="L93" s="3">
-        <v>46152.424618055556</v>
+        <v>20</v>
+      </c>
+      <c r="L93" s="2">
+        <v>46155.02822916667</v>
       </c>
       <c r="M93" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:14">
       <c r="A94" t="s">
         <v>106</v>
       </c>
@@ -5210,20 +5176,19 @@
         <v>1</v>
       </c>
       <c r="J94">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K94">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>46152.424629629633</v>
+        <v>20</v>
+      </c>
+      <c r="L94" s="2">
+        <v>46155.02824074074</v>
       </c>
       <c r="M94" t="s">
         <v>241</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1"/>
     <hyperlink ref="B3" r:id="rId2"/>
